--- a/backend/src/db/demo-docs/measurements-long-sleeve-training-tee.xlsx
+++ b/backend/src/db/demo-docs/measurements-long-sleeve-training-tee.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>24.5</v>
       </c>
     </row>
@@ -778,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -839,19 +845,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -868,19 +877,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>17.5</v>
       </c>
     </row>
@@ -961,19 +973,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>29.5</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>30.5</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>31.5</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>32.5</v>
       </c>
     </row>
@@ -990,19 +1005,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="F23" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>44</v>
       </c>
     </row>
@@ -1019,7 +1037,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -1032,6 +1050,9 @@
         <v>2</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1080,7 +1101,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -1093,6 +1114,9 @@
         <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>2</v>
       </c>
     </row>
